--- a/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
+++ b/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="492" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="492" uniqueCount="105">
   <si>
     <t>pull_item</t>
   </si>
@@ -301,9 +301,6 @@
   </si>
   <si>
     <t>tumpok</t>
-  </si>
-  <si>
-    <t>pieces</t>
   </si>
   <si>
     <t>pack</t>
@@ -393,13 +390,13 @@
         <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
         <v>104</v>
-      </c>
-      <c r="G1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2">
@@ -416,7 +413,7 @@
         <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -439,7 +436,7 @@
         <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -462,7 +459,7 @@
         <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -485,7 +482,7 @@
         <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -508,7 +505,7 @@
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -531,7 +528,7 @@
         <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -554,7 +551,7 @@
         <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
@@ -577,7 +574,7 @@
         <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F9" s="1">
         <v>3</v>
@@ -600,7 +597,7 @@
         <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
@@ -623,7 +620,7 @@
         <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -646,7 +643,7 @@
         <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
@@ -669,7 +666,7 @@
         <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F13" s="1">
         <v>3</v>
@@ -692,7 +689,7 @@
         <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -715,7 +712,7 @@
         <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" s="1">
         <v>3</v>
@@ -738,7 +735,7 @@
         <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -761,7 +758,7 @@
         <v>84</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -784,7 +781,7 @@
         <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F18" s="1">
         <v>3</v>
@@ -807,7 +804,7 @@
         <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
@@ -830,7 +827,7 @@
         <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
@@ -853,7 +850,7 @@
         <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
@@ -876,7 +873,7 @@
         <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
@@ -899,7 +896,7 @@
         <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
@@ -922,7 +919,7 @@
         <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -945,7 +942,7 @@
         <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
@@ -968,7 +965,7 @@
         <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F26" s="1">
         <v>2</v>
@@ -991,7 +988,7 @@
         <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="1">
         <v>2</v>
@@ -1014,7 +1011,7 @@
         <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
@@ -1037,7 +1034,7 @@
         <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F29" s="1">
         <v>3</v>
@@ -1060,7 +1057,7 @@
         <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1083,7 +1080,7 @@
         <v>85</v>
       </c>
       <c r="E31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F31" s="1">
         <v>3</v>
@@ -1106,7 +1103,7 @@
         <v>85</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1">
         <v>2</v>
@@ -1129,7 +1126,7 @@
         <v>90</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F33" s="1">
         <v>3</v>
@@ -1152,7 +1149,7 @@
         <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F34" s="1">
         <v>2</v>
@@ -1175,7 +1172,7 @@
         <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35" s="1">
         <v>3</v>
@@ -1198,7 +1195,7 @@
         <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F36" s="1">
         <v>3</v>
@@ -1221,7 +1218,7 @@
         <v>90</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F37" s="1">
         <v>3</v>
@@ -1244,7 +1241,7 @@
         <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F38" s="1">
         <v>3</v>
@@ -1267,7 +1264,7 @@
         <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -1290,7 +1287,7 @@
         <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F40" s="1">
         <v>3</v>
@@ -1313,7 +1310,7 @@
         <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="1">
         <v>3</v>
@@ -1336,7 +1333,7 @@
         <v>90</v>
       </c>
       <c r="E42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F42" s="1">
         <v>2</v>
@@ -1359,7 +1356,7 @@
         <v>88</v>
       </c>
       <c r="E43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F43" s="1">
         <v>2</v>
@@ -1382,7 +1379,7 @@
         <v>86</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F44" s="1">
         <v>3</v>
@@ -1405,7 +1402,7 @@
         <v>89</v>
       </c>
       <c r="E45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F45" s="1">
         <v>3</v>
@@ -1428,7 +1425,7 @@
         <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F46" s="1">
         <v>3</v>
@@ -1448,10 +1445,10 @@
         <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
@@ -1474,7 +1471,7 @@
         <v>85</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F48" s="1">
         <v>2</v>
@@ -1497,7 +1494,7 @@
         <v>89</v>
       </c>
       <c r="E49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F49" s="1">
         <v>3</v>
@@ -1517,10 +1514,10 @@
         <v>53</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F50" s="1">
         <v>3</v>
@@ -1540,10 +1537,10 @@
         <v>54</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F51" s="1">
         <v>3</v>
@@ -1566,7 +1563,7 @@
         <v>85</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="1">
         <v>2</v>
@@ -1589,7 +1586,7 @@
         <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F53" s="1">
         <v>2</v>
@@ -1612,7 +1609,7 @@
         <v>88</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F54" s="1">
         <v>3</v>
@@ -1635,7 +1632,7 @@
         <v>88</v>
       </c>
       <c r="E55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F55" s="1">
         <v>3</v>
@@ -1658,7 +1655,7 @@
         <v>95</v>
       </c>
       <c r="E56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F56" s="1">
         <v>3</v>
@@ -1678,10 +1675,10 @@
         <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F57" s="1">
         <v>2</v>
@@ -1704,7 +1701,7 @@
         <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F58" s="1">
         <v>2</v>
@@ -1727,7 +1724,7 @@
         <v>88</v>
       </c>
       <c r="E59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F59" s="1">
         <v>3</v>
@@ -1747,10 +1744,10 @@
         <v>60</v>
       </c>
       <c r="D60" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F60" s="1">
         <v>2</v>
@@ -1773,7 +1770,7 @@
         <v>85</v>
       </c>
       <c r="E61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F61" s="1">
         <v>2</v>
@@ -1796,7 +1793,7 @@
         <v>84</v>
       </c>
       <c r="E62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F62" s="1">
         <v>2</v>
@@ -1819,7 +1816,7 @@
         <v>85</v>
       </c>
       <c r="E63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F63" s="1">
         <v>3</v>
@@ -1839,10 +1836,10 @@
         <v>62</v>
       </c>
       <c r="D64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
@@ -1862,10 +1859,10 @@
         <v>63</v>
       </c>
       <c r="D65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F65" s="1">
         <v>3</v>
@@ -1888,7 +1885,7 @@
         <v>95</v>
       </c>
       <c r="E66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F66" s="1">
         <v>3</v>
@@ -1908,10 +1905,10 @@
         <v>63</v>
       </c>
       <c r="D67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F67" s="1">
         <v>3</v>
@@ -1934,7 +1931,7 @@
         <v>85</v>
       </c>
       <c r="E68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F68" s="1">
         <v>2</v>
@@ -1957,7 +1954,7 @@
         <v>84</v>
       </c>
       <c r="E69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F69" s="1">
         <v>3</v>
@@ -1980,7 +1977,7 @@
         <v>88</v>
       </c>
       <c r="E70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F70" s="1">
         <v>3</v>
@@ -2003,7 +2000,7 @@
         <v>84</v>
       </c>
       <c r="E71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F71" s="1">
         <v>2</v>
@@ -2026,7 +2023,7 @@
         <v>85</v>
       </c>
       <c r="E72" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F72" s="1">
         <v>2</v>
@@ -2049,7 +2046,7 @@
         <v>84</v>
       </c>
       <c r="E73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F73" s="1">
         <v>2</v>
@@ -2072,7 +2069,7 @@
         <v>85</v>
       </c>
       <c r="E74" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -2095,7 +2092,7 @@
         <v>85</v>
       </c>
       <c r="E75" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F75" s="1">
         <v>2</v>
@@ -2118,7 +2115,7 @@
         <v>89</v>
       </c>
       <c r="E76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F76" s="1">
         <v>3</v>
@@ -2138,10 +2135,10 @@
         <v>69</v>
       </c>
       <c r="D77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F77" s="1">
         <v>2</v>
@@ -2164,7 +2161,7 @@
         <v>88</v>
       </c>
       <c r="E78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F78" s="1">
         <v>3</v>
@@ -2187,7 +2184,7 @@
         <v>85</v>
       </c>
       <c r="E79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F79" s="1">
         <v>2</v>
@@ -2210,7 +2207,7 @@
         <v>95</v>
       </c>
       <c r="E80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F80" s="1">
         <v>3</v>
@@ -2233,7 +2230,7 @@
         <v>84</v>
       </c>
       <c r="E81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
@@ -2253,10 +2250,10 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E82" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F82" s="1">
         <v>3</v>
@@ -2279,7 +2276,7 @@
         <v>85</v>
       </c>
       <c r="E83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F83" s="1">
         <v>2</v>
@@ -2302,7 +2299,7 @@
         <v>90</v>
       </c>
       <c r="E84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F84" s="1">
         <v>2</v>
@@ -2325,7 +2322,7 @@
         <v>88</v>
       </c>
       <c r="E85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F85" s="1">
         <v>3</v>
@@ -2348,7 +2345,7 @@
         <v>85</v>
       </c>
       <c r="E86" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F86" s="1">
         <v>3</v>
@@ -2371,7 +2368,7 @@
         <v>85</v>
       </c>
       <c r="E87" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1">
         <v>2</v>
@@ -2394,7 +2391,7 @@
         <v>91</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F88" s="1">
         <v>3</v>
@@ -2414,10 +2411,10 @@
         <v>76</v>
       </c>
       <c r="D89" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F89" s="1">
         <v>2</v>
@@ -2440,7 +2437,7 @@
         <v>88</v>
       </c>
       <c r="E90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F90" s="1">
         <v>2</v>
@@ -2460,10 +2457,10 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F91" s="1">
         <v>3</v>
@@ -2483,10 +2480,10 @@
         <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F92" s="1">
         <v>3</v>
@@ -2509,7 +2506,7 @@
         <v>90</v>
       </c>
       <c r="E93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F93" s="1">
         <v>3</v>
@@ -2532,7 +2529,7 @@
         <v>89</v>
       </c>
       <c r="E94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F94" s="1">
         <v>3</v>
@@ -2555,7 +2552,7 @@
         <v>86</v>
       </c>
       <c r="E95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F95" s="1">
         <v>3</v>
@@ -2575,10 +2572,10 @@
         <v>81</v>
       </c>
       <c r="D96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F96" s="1">
         <v>3</v>
@@ -2601,7 +2598,7 @@
         <v>88</v>
       </c>
       <c r="E97" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F97" s="1">
         <v>3</v>
@@ -2624,7 +2621,7 @@
         <v>90</v>
       </c>
       <c r="E98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F98" s="1">
         <v>3</v>

--- a/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
+++ b/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="492" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="487" uniqueCount="105">
   <si>
     <t>pull_item</t>
   </si>
@@ -373,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1523,7 +1523,7 @@
         <v>3</v>
       </c>
       <c r="G50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1965,25 +1965,25 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B70" t="s">
         <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F70" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -1994,10 +1994,10 @@
         <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s">
         <v>101</v>
@@ -2020,7 +2020,7 @@
         <v>66</v>
       </c>
       <c r="D72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E72" t="s">
         <v>101</v>
@@ -2040,10 +2040,10 @@
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E73" t="s">
         <v>101</v>
@@ -2063,7 +2063,7 @@
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D74" t="s">
         <v>85</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B75" t="s">
         <v>18</v>
@@ -2089,44 +2089,44 @@
         <v>68</v>
       </c>
       <c r="D75" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E75" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F75" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D76" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E76" t="s">
         <v>102</v>
       </c>
       <c r="F76" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B77" t="s">
         <v>18</v>
@@ -2135,36 +2135,36 @@
         <v>69</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E77" t="s">
         <v>102</v>
       </c>
       <c r="F77" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B78" t="s">
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D78" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F78" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
@@ -2181,67 +2181,67 @@
         <v>70</v>
       </c>
       <c r="D79" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E79" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F79" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D80" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F80" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D81" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E81" t="s">
         <v>101</v>
       </c>
       <c r="F81" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
@@ -2250,102 +2250,102 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E82" t="s">
         <v>101</v>
       </c>
       <c r="F82" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B83" t="s">
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F83" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G83" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B84" t="s">
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E84" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F84" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D85" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E85" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F85" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G85" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D86" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E86" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F86" s="1">
         <v>3</v>
@@ -2356,16 +2356,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D87" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E87" t="s">
         <v>101</v>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B88" t="s">
         <v>18</v>
       </c>
       <c r="C88" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D88" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E88" t="s">
         <v>102</v>
@@ -2402,19 +2402,19 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B89" t="s">
         <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D89" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E89" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F89" s="1">
         <v>2</v>
@@ -2425,30 +2425,30 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E90" t="s">
         <v>102</v>
       </c>
       <c r="F90" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
         <v>19</v>
@@ -2457,7 +2457,7 @@
         <v>78</v>
       </c>
       <c r="D91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E91" t="s">
         <v>102</v>
@@ -2471,16 +2471,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B92" t="s">
         <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D92" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E92" t="s">
         <v>102</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B93" t="s">
         <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E93" t="s">
         <v>102</v>
@@ -2517,19 +2517,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B94" t="s">
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D94" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E94" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F94" s="1">
         <v>3</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
         <v>19</v>
@@ -2549,10 +2549,10 @@
         <v>81</v>
       </c>
       <c r="D95" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E95" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F95" s="1">
         <v>3</v>
@@ -2563,16 +2563,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B96" t="s">
         <v>19</v>
       </c>
       <c r="C96" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E96" t="s">
         <v>102</v>
@@ -2586,16 +2586,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B97" t="s">
         <v>19</v>
       </c>
       <c r="C97" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D97" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E97" t="s">
         <v>102</v>
@@ -2604,29 +2604,6 @@
         <v>3</v>
       </c>
       <c r="G97" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>2</v>
-      </c>
-      <c r="B98" t="s">
-        <v>19</v>
-      </c>
-      <c r="C98" t="s">
-        <v>82</v>
-      </c>
-      <c r="D98" t="s">
-        <v>90</v>
-      </c>
-      <c r="E98" t="s">
-        <v>102</v>
-      </c>
-      <c r="F98" s="1">
-        <v>3</v>
-      </c>
-      <c r="G98" s="1">
         <v>2</v>
       </c>
     </row>

--- a/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
+++ b/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="487" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="477" uniqueCount="105">
   <si>
     <t>pull_item</t>
   </si>
@@ -373,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,7 +999,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1008,10 +1008,10 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
@@ -1022,19 +1022,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F29" s="1">
         <v>3</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -1054,10 +1054,10 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1074,7 +1074,7 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
         <v>85</v>
@@ -1083,38 +1083,38 @@
         <v>101</v>
       </c>
       <c r="F31" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -1123,56 +1123,56 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E34" t="s">
         <v>101</v>
       </c>
       <c r="F34" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F35" s="1">
         <v>3</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
@@ -1192,7 +1192,7 @@
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
         <v>102</v>
@@ -1215,7 +1215,7 @@
         <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
         <v>102</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
@@ -1238,7 +1238,7 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E38" t="s">
         <v>102</v>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -1261,7 +1261,7 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E39" t="s">
         <v>102</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>18</v>
@@ -1284,7 +1284,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
         <v>102</v>
@@ -1298,25 +1298,25 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
         <v>102</v>
       </c>
       <c r="F41" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1330,10 +1330,10 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42" s="1">
         <v>2</v>
@@ -1350,36 +1350,36 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E43" t="s">
         <v>101</v>
       </c>
       <c r="F43" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F44" s="1">
         <v>3</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
@@ -1399,10 +1399,10 @@
         <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F45" s="1">
         <v>3</v>
@@ -1419,7 +1419,7 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
         <v>85</v>
@@ -1428,27 +1428,27 @@
         <v>101</v>
       </c>
       <c r="F46" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B47" t="s">
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
@@ -1459,39 +1459,39 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B48" t="s">
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F48" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
         <v>102</v>
@@ -1505,99 +1505,99 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F50" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F51" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E52" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F53" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
@@ -1606,10 +1606,10 @@
         <v>57</v>
       </c>
       <c r="D54" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F54" s="1">
         <v>3</v>
@@ -1626,79 +1626,79 @@
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E55" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F55" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B56" t="s">
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F56" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D57" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E57" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E58" t="s">
         <v>101</v>
@@ -1712,39 +1712,39 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F59" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D60" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E60" t="s">
         <v>101</v>
@@ -1764,7 +1764,7 @@
         <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D61" t="s">
         <v>85</v>
@@ -1773,50 +1773,50 @@
         <v>101</v>
       </c>
       <c r="F61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E62" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B63" t="s">
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D63" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E63" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F63" s="1">
         <v>3</v>
@@ -1827,16 +1827,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
         <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E64" t="s">
         <v>102</v>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65" t="s">
         <v>18</v>
@@ -1859,7 +1859,7 @@
         <v>63</v>
       </c>
       <c r="D65" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E65" t="s">
         <v>102</v>
@@ -1873,42 +1873,42 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B66" t="s">
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D66" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F66" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B67" t="s">
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D67" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E67" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F67" s="1">
         <v>3</v>
@@ -1925,10 +1925,10 @@
         <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E68" t="s">
         <v>101</v>
@@ -1948,19 +1948,19 @@
         <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E69" t="s">
         <v>101</v>
       </c>
       <c r="F69" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -1971,7 +1971,7 @@
         <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D70" t="s">
         <v>84</v>
@@ -1994,7 +1994,7 @@
         <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D71" t="s">
         <v>85</v>
@@ -2017,10 +2017,10 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D72" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E72" t="s">
         <v>101</v>
@@ -2034,42 +2034,42 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B73" t="s">
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D73" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E73" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F73" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B74" t="s">
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D74" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -2086,10 +2086,10 @@
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E75" t="s">
         <v>102</v>
@@ -2103,19 +2103,19 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D76" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F76" s="1">
         <v>2</v>
@@ -2126,16 +2126,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D77" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E77" t="s">
         <v>102</v>
@@ -2155,10 +2155,10 @@
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E78" t="s">
         <v>101</v>
@@ -2172,19 +2172,19 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F79" s="1">
         <v>3</v>
@@ -2201,10 +2201,10 @@
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E80" t="s">
         <v>101</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B81" t="s">
         <v>18</v>
@@ -2230,53 +2230,53 @@
         <v>90</v>
       </c>
       <c r="E81" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F81" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D82" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E82" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F82" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B83" t="s">
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D83" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F83" s="1">
         <v>3</v>
@@ -2293,7 +2293,7 @@
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D84" t="s">
         <v>85</v>
@@ -2302,15 +2302,15 @@
         <v>101</v>
       </c>
       <c r="F84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G84" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
@@ -2319,56 +2319,56 @@
         <v>75</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E85" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F85" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E86" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F86" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G86" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D87" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E87" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F87" s="1">
         <v>2</v>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D88" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E88" t="s">
         <v>102</v>
@@ -2402,39 +2402,39 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C89" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D89" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E89" t="s">
         <v>102</v>
       </c>
       <c r="F89" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B90" t="s">
         <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D90" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E90" t="s">
         <v>102</v>
@@ -2448,16 +2448,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B91" t="s">
         <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D91" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E91" t="s">
         <v>102</v>
@@ -2471,19 +2471,19 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B92" t="s">
         <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D92" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F92" s="1">
         <v>3</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B93" t="s">
         <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D93" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E93" t="s">
         <v>102</v>
@@ -2517,19 +2517,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B94" t="s">
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D94" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E94" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F94" s="1">
         <v>3</v>
@@ -2540,16 +2540,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
         <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D95" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E95" t="s">
         <v>102</v>
@@ -2558,52 +2558,6 @@
         <v>3</v>
       </c>
       <c r="G95" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>4</v>
-      </c>
-      <c r="B96" t="s">
-        <v>19</v>
-      </c>
-      <c r="C96" t="s">
-        <v>71</v>
-      </c>
-      <c r="D96" t="s">
-        <v>88</v>
-      </c>
-      <c r="E96" t="s">
-        <v>102</v>
-      </c>
-      <c r="F96" s="1">
-        <v>3</v>
-      </c>
-      <c r="G96" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>2</v>
-      </c>
-      <c r="B97" t="s">
-        <v>19</v>
-      </c>
-      <c r="C97" t="s">
-        <v>82</v>
-      </c>
-      <c r="D97" t="s">
-        <v>90</v>
-      </c>
-      <c r="E97" t="s">
-        <v>102</v>
-      </c>
-      <c r="F97" s="1">
-        <v>3</v>
-      </c>
-      <c r="G97" s="1">
         <v>2</v>
       </c>
     </row>

--- a/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
+++ b/outputs/build/diagnostics/ref_underfilled_sizes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="477" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="442" uniqueCount="104">
   <si>
     <t>pull_item</t>
   </si>
@@ -162,9 +162,6 @@
     <t>ALIMODIAN</t>
   </si>
   <si>
-    <t>ANILAO</t>
-  </si>
-  <si>
     <t>BALASAN</t>
   </si>
   <si>
@@ -234,15 +231,15 @@
     <t>SAN JOAQUIN</t>
   </si>
   <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
     <t>SANTA BARBARA</t>
   </si>
   <si>
     <t>SARA</t>
   </si>
   <si>
+    <t>TIGBAUAN</t>
+  </si>
+  <si>
     <t>TUBUNGAN</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
     <t>PONTEVEDRA</t>
   </si>
   <si>
-    <t>VALLADOLID</t>
-  </si>
-  <si>
     <t>harmonized_nsu_unit</t>
   </si>
   <si>
@@ -313,6 +307,9 @@
   </si>
   <si>
     <t>whole (chicken)</t>
+  </si>
+  <si>
+    <t>gallons</t>
   </si>
   <si>
     <t>corrected_unit</t>
@@ -373,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -387,16 +384,16 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" t="s">
         <v>103</v>
-      </c>
-      <c r="G1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2">
@@ -410,10 +407,10 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1">
         <v>3</v>
@@ -433,10 +430,10 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -456,10 +453,10 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -479,10 +476,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
@@ -502,10 +499,10 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -525,10 +522,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -548,10 +545,10 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
@@ -571,10 +568,10 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F9" s="1">
         <v>3</v>
@@ -594,10 +591,10 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
@@ -617,10 +614,10 @@
         <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -640,10 +637,10 @@
         <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F12" s="1">
         <v>3</v>
@@ -663,10 +660,10 @@
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
         <v>3</v>
@@ -686,10 +683,10 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -709,10 +706,10 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F15" s="1">
         <v>3</v>
@@ -732,10 +729,10 @@
         <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -755,10 +752,10 @@
         <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -778,10 +775,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F18" s="1">
         <v>3</v>
@@ -801,10 +798,10 @@
         <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F19" s="1">
         <v>3</v>
@@ -824,10 +821,10 @@
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F20" s="1">
         <v>3</v>
@@ -847,10 +844,10 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
@@ -870,10 +867,10 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="1">
         <v>3</v>
@@ -893,10 +890,10 @@
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
@@ -916,10 +913,10 @@
         <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="1">
         <v>3</v>
@@ -939,10 +936,10 @@
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="1">
         <v>2</v>
@@ -962,10 +959,10 @@
         <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1">
         <v>2</v>
@@ -985,10 +982,10 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="1">
         <v>2</v>
@@ -1008,10 +1005,10 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
@@ -1031,10 +1028,10 @@
         <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F29" s="1">
         <v>3</v>
@@ -1054,10 +1051,10 @@
         <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F30" s="1">
         <v>3</v>
@@ -1077,10 +1074,10 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1">
         <v>2</v>
@@ -1100,10 +1097,10 @@
         <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1">
         <v>3</v>
@@ -1123,10 +1120,10 @@
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F33" s="1">
         <v>2</v>
@@ -1146,10 +1143,10 @@
         <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F34" s="1">
         <v>3</v>
@@ -1169,10 +1166,10 @@
         <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35" s="1">
         <v>3</v>
@@ -1192,10 +1189,10 @@
         <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F36" s="1">
         <v>3</v>
@@ -1215,10 +1212,10 @@
         <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F37" s="1">
         <v>3</v>
@@ -1238,10 +1235,10 @@
         <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F38" s="1">
         <v>3</v>
@@ -1261,10 +1258,10 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -1284,10 +1281,10 @@
         <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F40" s="1">
         <v>3</v>
@@ -1307,10 +1304,10 @@
         <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F41" s="1">
         <v>2</v>
@@ -1321,30 +1318,30 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" t="s">
         <v>101</v>
       </c>
       <c r="F42" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
         <v>18</v>
@@ -1353,10 +1350,10 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" s="1">
         <v>3</v>
@@ -1367,7 +1364,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
@@ -1376,30 +1373,30 @@
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F44" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E45" t="s">
         <v>101</v>
@@ -1413,42 +1410,42 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E46" t="s">
         <v>101</v>
       </c>
       <c r="F46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B47" t="s">
         <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F47" s="1">
         <v>3</v>
@@ -1459,88 +1456,88 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
         <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F48" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F49" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
         <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E50" t="s">
         <v>101</v>
       </c>
       <c r="F50" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
         <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1">
         <v>2</v>
@@ -1551,7 +1548,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
@@ -1560,33 +1557,33 @@
         <v>57</v>
       </c>
       <c r="D52" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F52" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F53" s="1">
         <v>3</v>
@@ -1597,42 +1594,42 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D54" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F55" s="1">
         <v>2</v>
@@ -1649,13 +1646,13 @@
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F56" s="1">
         <v>2</v>
@@ -1666,19 +1663,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F57" s="1">
         <v>3</v>
@@ -1689,76 +1686,76 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E58" t="s">
         <v>101</v>
       </c>
       <c r="F58" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E59" t="s">
         <v>101</v>
       </c>
       <c r="F59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D60" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E60" t="s">
         <v>101</v>
       </c>
       <c r="F60" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
@@ -1767,7 +1764,7 @@
         <v>62</v>
       </c>
       <c r="D61" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E61" t="s">
         <v>101</v>
@@ -1781,30 +1778,30 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D62" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E62" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F62" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
         <v>18</v>
@@ -1813,10 +1810,10 @@
         <v>63</v>
       </c>
       <c r="D63" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E63" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F63" s="1">
         <v>3</v>
@@ -1827,48 +1824,48 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B64" t="s">
         <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D64" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E64" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F64" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B65" t="s">
         <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D65" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E65" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F65" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1879,13 +1876,13 @@
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D66" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F66" s="1">
         <v>2</v>
@@ -1902,19 +1899,19 @@
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F67" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -1925,13 +1922,13 @@
         <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F68" s="1">
         <v>2</v>
@@ -1942,48 +1939,48 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B69" t="s">
         <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E69" t="s">
         <v>101</v>
       </c>
       <c r="F69" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B70" t="s">
         <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D70" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E70" t="s">
         <v>101</v>
       </c>
       <c r="F70" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -1994,13 +1991,13 @@
         <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D71" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F71" s="1">
         <v>2</v>
@@ -2011,108 +2008,108 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D72" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
         <v>101</v>
       </c>
       <c r="F72" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B73" t="s">
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D73" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E73" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F73" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G73" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
         <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D74" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E74" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B75" t="s">
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D75" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E75" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F75" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D76" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E76" t="s">
         <v>101</v>
@@ -2126,19 +2123,19 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B77" t="s">
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D77" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E77" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F77" s="1">
         <v>3</v>
@@ -2155,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E78" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F78" s="1">
         <v>2</v>
@@ -2172,16 +2169,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E79" t="s">
         <v>101</v>
@@ -2195,42 +2192,42 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D80" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E80" t="s">
         <v>101</v>
       </c>
       <c r="F80" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D81" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E81" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
@@ -2241,39 +2238,39 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D82" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E82" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F82" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C83" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E83" t="s">
         <v>101</v>
@@ -2287,42 +2284,42 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C84" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D84" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E84" t="s">
         <v>101</v>
       </c>
       <c r="F84" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C85" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D85" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E85" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F85" s="1">
         <v>3</v>
@@ -2333,231 +2330,70 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C86" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D86" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E86" t="s">
         <v>101</v>
       </c>
       <c r="F86" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C87" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D87" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E87" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F87" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B88" t="s">
         <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E88" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F88" s="1">
         <v>3</v>
       </c>
       <c r="G88" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" t="s">
-        <v>19</v>
-      </c>
-      <c r="C89" t="s">
-        <v>78</v>
-      </c>
-      <c r="D89" t="s">
-        <v>98</v>
-      </c>
-      <c r="E89" t="s">
-        <v>102</v>
-      </c>
-      <c r="F89" s="1">
-        <v>3</v>
-      </c>
-      <c r="G89" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>6</v>
-      </c>
-      <c r="B90" t="s">
-        <v>19</v>
-      </c>
-      <c r="C90" t="s">
-        <v>79</v>
-      </c>
-      <c r="D90" t="s">
-        <v>90</v>
-      </c>
-      <c r="E90" t="s">
-        <v>102</v>
-      </c>
-      <c r="F90" s="1">
-        <v>3</v>
-      </c>
-      <c r="G90" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>5</v>
-      </c>
-      <c r="B91" t="s">
-        <v>19</v>
-      </c>
-      <c r="C91" t="s">
-        <v>80</v>
-      </c>
-      <c r="D91" t="s">
-        <v>89</v>
-      </c>
-      <c r="E91" t="s">
-        <v>102</v>
-      </c>
-      <c r="F91" s="1">
-        <v>3</v>
-      </c>
-      <c r="G91" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>2</v>
-      </c>
-      <c r="B92" t="s">
-        <v>19</v>
-      </c>
-      <c r="C92" t="s">
-        <v>81</v>
-      </c>
-      <c r="D92" t="s">
-        <v>86</v>
-      </c>
-      <c r="E92" t="s">
-        <v>101</v>
-      </c>
-      <c r="F92" s="1">
-        <v>3</v>
-      </c>
-      <c r="G92" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>7</v>
-      </c>
-      <c r="B93" t="s">
-        <v>19</v>
-      </c>
-      <c r="C93" t="s">
-        <v>81</v>
-      </c>
-      <c r="D93" t="s">
-        <v>98</v>
-      </c>
-      <c r="E93" t="s">
-        <v>102</v>
-      </c>
-      <c r="F93" s="1">
-        <v>3</v>
-      </c>
-      <c r="G93" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>4</v>
-      </c>
-      <c r="B94" t="s">
-        <v>19</v>
-      </c>
-      <c r="C94" t="s">
-        <v>71</v>
-      </c>
-      <c r="D94" t="s">
-        <v>88</v>
-      </c>
-      <c r="E94" t="s">
-        <v>102</v>
-      </c>
-      <c r="F94" s="1">
-        <v>3</v>
-      </c>
-      <c r="G94" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>2</v>
-      </c>
-      <c r="B95" t="s">
-        <v>19</v>
-      </c>
-      <c r="C95" t="s">
-        <v>82</v>
-      </c>
-      <c r="D95" t="s">
-        <v>90</v>
-      </c>
-      <c r="E95" t="s">
-        <v>102</v>
-      </c>
-      <c r="F95" s="1">
-        <v>3</v>
-      </c>
-      <c r="G95" s="1">
         <v>2</v>
       </c>
     </row>
